--- a/Soft skills/Words.xlsx
+++ b/Soft skills/Words.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Working\Java Full Stack\Soft skills\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B431F5D-0A95-4EC0-8943-DEAB732B10AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6841163-43C6-472F-8C0B-A167DBDA7716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57107928-2823-472E-8A6E-F1A53761FD58}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="297">
   <si>
     <t>Word</t>
   </si>
@@ -514,6 +514,408 @@
   </si>
   <si>
     <t>crimes will confine your freedoms</t>
+  </si>
+  <si>
+    <t>obvious</t>
+  </si>
+  <si>
+    <t>must</t>
+  </si>
+  <si>
+    <t>should have</t>
+  </si>
+  <si>
+    <t>unobvious</t>
+  </si>
+  <si>
+    <t>not sure</t>
+  </si>
+  <si>
+    <t>invisible</t>
+  </si>
+  <si>
+    <t>to develop a good habbit we need to make its clues more obvious</t>
+  </si>
+  <si>
+    <t>if you want to get ride of a bad habbit then make it invisible</t>
+  </si>
+  <si>
+    <t>get ride of</t>
+  </si>
+  <si>
+    <t>delete</t>
+  </si>
+  <si>
+    <t>to cut down</t>
+  </si>
+  <si>
+    <t>to curb down</t>
+  </si>
+  <si>
+    <t>to leave</t>
+  </si>
+  <si>
+    <t>to release</t>
+  </si>
+  <si>
+    <t>to escape</t>
+  </si>
+  <si>
+    <t>dropout</t>
+  </si>
+  <si>
+    <t>to call off</t>
+  </si>
+  <si>
+    <t>to cancel</t>
+  </si>
+  <si>
+    <t>patchup</t>
+  </si>
+  <si>
+    <t>to stay with</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> to connect with</t>
+  </si>
+  <si>
+    <t>add on</t>
+  </si>
+  <si>
+    <t>To keep</t>
+  </si>
+  <si>
+    <t>To mainten</t>
+  </si>
+  <si>
+    <t>We are trying to get ride of useless screen time</t>
+  </si>
+  <si>
+    <t>I tried to cut down conversiation because of wasting time in meeting</t>
+  </si>
+  <si>
+    <t>Police incountered criminal to get ride of daily food waste</t>
+  </si>
+  <si>
+    <t>he dropout the gun to show how scared he is</t>
+  </si>
+  <si>
+    <t>I got to ride off my game playing habbit</t>
+  </si>
+  <si>
+    <t>curl down</t>
+  </si>
+  <si>
+    <t>imbibe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">we are trying to imbibe good habbits to </t>
+  </si>
+  <si>
+    <t>truncate</t>
+  </si>
+  <si>
+    <t>Somethings is life need to be truncate permenantly</t>
+  </si>
+  <si>
+    <t>vanish</t>
+  </si>
+  <si>
+    <t>We use truncate as a command to delete things permenetly</t>
+  </si>
+  <si>
+    <t>Care vanished in crowd party</t>
+  </si>
+  <si>
+    <t>Let's cut it off</t>
+  </si>
+  <si>
+    <t>Try to cut off from situation which might not be right for you</t>
+  </si>
+  <si>
+    <t>Block</t>
+  </si>
+  <si>
+    <t>We are trying to patchup with pakistan</t>
+  </si>
+  <si>
+    <t>Patch up</t>
+  </si>
+  <si>
+    <t>Rebuilding</t>
+  </si>
+  <si>
+    <t>rejoining</t>
+  </si>
+  <si>
+    <t>we are trying to patch us with them</t>
+  </si>
+  <si>
+    <t>Align with</t>
+  </si>
+  <si>
+    <t>connect with</t>
+  </si>
+  <si>
+    <t>mixup with</t>
+  </si>
+  <si>
+    <t>sycronize</t>
+  </si>
+  <si>
+    <t>configure with</t>
+  </si>
+  <si>
+    <t>meditation is a practice of configuring with soul</t>
+  </si>
+  <si>
+    <t>We are trying to sycronize with nabours</t>
+  </si>
+  <si>
+    <t>Disconnect</t>
+  </si>
+  <si>
+    <t>Break</t>
+  </si>
+  <si>
+    <t>allies</t>
+  </si>
+  <si>
+    <t>none allies</t>
+  </si>
+  <si>
+    <t>india has a none allies polacy in geopolatics</t>
+  </si>
+  <si>
+    <t>Align</t>
+  </si>
+  <si>
+    <t>Allies</t>
+  </si>
+  <si>
+    <t>ally</t>
+  </si>
+  <si>
+    <t>we are trying to join hands with vocabulary</t>
+  </si>
+  <si>
+    <t>unanswered</t>
+  </si>
+  <si>
+    <t>unaddressed</t>
+  </si>
+  <si>
+    <t>unstone</t>
+  </si>
+  <si>
+    <t>untouched</t>
+  </si>
+  <si>
+    <t>left out</t>
+  </si>
+  <si>
+    <t>have we left out anything</t>
+  </si>
+  <si>
+    <t>are you missing out on something</t>
+  </si>
+  <si>
+    <t>are you leaving out on something</t>
+  </si>
+  <si>
+    <t>missing out</t>
+  </si>
+  <si>
+    <t>inferior</t>
+  </si>
+  <si>
+    <t>Radiation</t>
+  </si>
+  <si>
+    <t>energy</t>
+  </si>
+  <si>
+    <t>spirit</t>
+  </si>
+  <si>
+    <t>embark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">go on </t>
+  </si>
+  <si>
+    <t>go ahead</t>
+  </si>
+  <si>
+    <t>lets start</t>
+  </si>
+  <si>
+    <t>lets move forward</t>
+  </si>
+  <si>
+    <t>dive into</t>
+  </si>
+  <si>
+    <t>march a head</t>
+  </si>
+  <si>
+    <t>step back</t>
+  </si>
+  <si>
+    <t>fall back</t>
+  </si>
+  <si>
+    <t>backward</t>
+  </si>
+  <si>
+    <t>pull back</t>
+  </si>
+  <si>
+    <t>fall down</t>
+  </si>
+  <si>
+    <t>stop</t>
+  </si>
+  <si>
+    <t>embarked</t>
+  </si>
+  <si>
+    <t>embarking</t>
+  </si>
+  <si>
+    <t>proceed</t>
+  </si>
+  <si>
+    <t>lets embark on this beautiful jurney</t>
+  </si>
+  <si>
+    <t>we are embarking on the juarney of recognizing words</t>
+  </si>
+  <si>
+    <t>opt</t>
+  </si>
+  <si>
+    <t>choose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">select </t>
+  </si>
+  <si>
+    <t>decide</t>
+  </si>
+  <si>
+    <t>pick</t>
+  </si>
+  <si>
+    <t>mark</t>
+  </si>
+  <si>
+    <t>prefere</t>
+  </si>
+  <si>
+    <t>priortise</t>
+  </si>
+  <si>
+    <t>pinpoint</t>
+  </si>
+  <si>
+    <t>opted</t>
+  </si>
+  <si>
+    <t>opts</t>
+  </si>
+  <si>
+    <t>indea opts to bat first</t>
+  </si>
+  <si>
+    <t>option</t>
+  </si>
+  <si>
+    <t>dew</t>
+  </si>
+  <si>
+    <t>water droplets</t>
+  </si>
+  <si>
+    <t>due</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>duo</t>
+  </si>
+  <si>
+    <t>mindfull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">means </t>
+  </si>
+  <si>
+    <t>aware</t>
+  </si>
+  <si>
+    <t>carefull</t>
+  </si>
+  <si>
+    <t>watchfull</t>
+  </si>
+  <si>
+    <t>visualant</t>
+  </si>
+  <si>
+    <t>attentive</t>
+  </si>
+  <si>
+    <t>balanced</t>
+  </si>
+  <si>
+    <t>careless</t>
+  </si>
+  <si>
+    <t>unaware</t>
+  </si>
+  <si>
+    <t>mindless</t>
+  </si>
+  <si>
+    <t>irresponsible</t>
+  </si>
+  <si>
+    <t>responsible</t>
+  </si>
+  <si>
+    <t>We need to be mindfull with our actions</t>
+  </si>
+  <si>
+    <t>he need to be mindfull with upcoming obstacles</t>
+  </si>
+  <si>
+    <t>we must be mindfull with entire project idea</t>
+  </si>
+  <si>
+    <t>discrimination</t>
+  </si>
+  <si>
+    <t>discriminate</t>
+  </si>
+  <si>
+    <t>prevalent</t>
+  </si>
+  <si>
+    <t>popular</t>
+  </si>
+  <si>
+    <t>well known</t>
+  </si>
+  <si>
+    <t>profound</t>
+  </si>
+  <si>
+    <t>He were not that prevalent in the past for that book</t>
+  </si>
+  <si>
+    <t>His idea were not prevalent</t>
   </si>
 </sst>
 </file>
@@ -880,16 +1282,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61498B0B-65E1-41EE-BDA5-1E9C4DD906D3}">
-  <dimension ref="A1:G273"/>
+  <dimension ref="A1:N273"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="68.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="63.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="42.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="51.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="51.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="33.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -1751,503 +2159,917 @@
       <c r="A108" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B108" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B109" t="s">
+        <v>164</v>
+      </c>
+      <c r="C109" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B110" t="s">
+        <v>166</v>
+      </c>
+      <c r="C110" t="s">
+        <v>167</v>
+      </c>
+      <c r="D110" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B111" t="s">
+        <v>169</v>
+      </c>
+      <c r="C111" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B115" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B116" t="s">
+        <v>172</v>
+      </c>
+      <c r="C116" t="s">
+        <v>173</v>
+      </c>
+      <c r="D116" t="s">
+        <v>174</v>
+      </c>
+      <c r="E116" t="s">
+        <v>175</v>
+      </c>
+      <c r="F116" t="s">
+        <v>176</v>
+      </c>
+      <c r="G116" t="s">
+        <v>177</v>
+      </c>
+      <c r="H116" t="s">
+        <v>178</v>
+      </c>
+      <c r="I116" t="s">
+        <v>179</v>
+      </c>
+      <c r="J116" t="s">
+        <v>180</v>
+      </c>
+      <c r="K116" t="s">
+        <v>193</v>
+      </c>
+      <c r="L116" t="s">
+        <v>195</v>
+      </c>
+      <c r="M116" t="s">
+        <v>197</v>
+      </c>
+      <c r="N116" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B117" t="s">
+        <v>181</v>
+      </c>
+      <c r="C117" t="s">
+        <v>182</v>
+      </c>
+      <c r="D117" t="s">
+        <v>183</v>
+      </c>
+      <c r="E117" t="s">
+        <v>184</v>
+      </c>
+      <c r="F117" t="s">
+        <v>185</v>
+      </c>
+      <c r="G117" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B118" t="s">
+        <v>187</v>
+      </c>
+      <c r="C118" t="s">
+        <v>188</v>
+      </c>
+      <c r="D118" t="s">
+        <v>191</v>
+      </c>
+      <c r="E118" t="s">
+        <v>189</v>
+      </c>
+      <c r="F118" t="s">
+        <v>190</v>
+      </c>
+      <c r="G118" t="s">
+        <v>194</v>
+      </c>
+      <c r="H118" t="s">
+        <v>196</v>
+      </c>
+      <c r="I118" t="s">
+        <v>198</v>
+      </c>
+      <c r="J118" t="s">
+        <v>199</v>
+      </c>
+      <c r="K118" t="s">
+        <v>200</v>
+      </c>
+      <c r="L118" t="s">
+        <v>201</v>
+      </c>
+      <c r="M118" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B122" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B129" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B130" t="s">
+        <v>205</v>
+      </c>
+      <c r="C130" t="s">
+        <v>206</v>
+      </c>
+      <c r="D130" t="s">
+        <v>208</v>
+      </c>
+      <c r="E130" t="s">
+        <v>209</v>
+      </c>
+      <c r="F130" t="s">
+        <v>210</v>
+      </c>
+      <c r="G130" t="s">
+        <v>211</v>
+      </c>
+      <c r="H130" t="s">
+        <v>212</v>
+      </c>
+      <c r="I130" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B131" t="s">
+        <v>215</v>
+      </c>
+      <c r="C131" t="s">
+        <v>216</v>
+      </c>
+      <c r="D131" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B132" t="s">
+        <v>207</v>
+      </c>
+      <c r="C132" t="s">
+        <v>213</v>
+      </c>
+      <c r="D132" t="s">
+        <v>214</v>
+      </c>
+      <c r="E132" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B136" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B139" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B140" t="s">
+        <v>221</v>
+      </c>
+      <c r="C140" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B143" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B144" t="s">
+        <v>225</v>
+      </c>
+      <c r="C144" t="s">
+        <v>226</v>
+      </c>
+      <c r="D144" t="s">
+        <v>227</v>
+      </c>
+      <c r="E144" t="s">
+        <v>228</v>
+      </c>
+      <c r="F144" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B145" t="s">
+        <v>229</v>
+      </c>
+      <c r="C145" t="s">
+        <v>230</v>
+      </c>
+      <c r="D145" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B150" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B157" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B158" t="s">
+        <v>235</v>
+      </c>
+      <c r="C158" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B164" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B165" t="s">
+        <v>238</v>
+      </c>
+      <c r="C165" t="s">
+        <v>239</v>
+      </c>
+      <c r="D165" t="s">
+        <v>240</v>
+      </c>
+      <c r="E165" t="s">
+        <v>241</v>
+      </c>
+      <c r="F165" t="s">
+        <v>242</v>
+      </c>
+      <c r="G165" t="s">
+        <v>243</v>
+      </c>
+      <c r="H165" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B166" t="s">
+        <v>244</v>
+      </c>
+      <c r="C166" t="s">
+        <v>245</v>
+      </c>
+      <c r="D166" t="s">
+        <v>246</v>
+      </c>
+      <c r="E166" t="s">
+        <v>247</v>
+      </c>
+      <c r="F166" t="s">
+        <v>248</v>
+      </c>
+      <c r="G166" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B167" t="s">
+        <v>253</v>
+      </c>
+      <c r="C167" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B169" t="s">
+        <v>237</v>
+      </c>
+      <c r="C169" t="s">
+        <v>250</v>
+      </c>
+      <c r="D169" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B171" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B172" t="s">
+        <v>256</v>
+      </c>
+      <c r="C172" t="s">
+        <v>257</v>
+      </c>
+      <c r="D172" t="s">
+        <v>258</v>
+      </c>
+      <c r="E172" t="s">
+        <v>259</v>
+      </c>
+      <c r="F172" t="s">
+        <v>260</v>
+      </c>
+      <c r="G172" t="s">
+        <v>261</v>
+      </c>
+      <c r="H172" t="s">
+        <v>262</v>
+      </c>
+      <c r="I172" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B174" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B176" t="s">
+        <v>255</v>
+      </c>
+      <c r="C176" t="s">
+        <v>264</v>
+      </c>
+      <c r="D176" t="s">
+        <v>265</v>
+      </c>
+      <c r="E176" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B178" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B179" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B185" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B186" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B192" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B199" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B200" t="s">
+        <v>274</v>
+      </c>
+      <c r="C200" t="s">
+        <v>275</v>
+      </c>
+      <c r="D200" t="s">
+        <v>276</v>
+      </c>
+      <c r="E200" t="s">
+        <v>277</v>
+      </c>
+      <c r="F200" t="s">
+        <v>278</v>
+      </c>
+      <c r="G200" t="s">
+        <v>279</v>
+      </c>
+      <c r="H200" t="s">
+        <v>280</v>
+      </c>
+      <c r="I200" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B201" t="s">
+        <v>281</v>
+      </c>
+      <c r="C201" t="s">
+        <v>282</v>
+      </c>
+      <c r="D201" t="s">
+        <v>283</v>
+      </c>
+      <c r="E201" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B202" t="s">
+        <v>286</v>
+      </c>
+      <c r="C202" t="s">
+        <v>287</v>
+      </c>
+      <c r="D202" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B206" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B207" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B210" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B211" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B213" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B214" t="s">
+        <v>292</v>
+      </c>
+      <c r="C214" t="s">
+        <v>293</v>
+      </c>
+      <c r="D214" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B216" t="s">
+        <v>295</v>
+      </c>
+      <c r="C216" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>45</v>
       </c>

--- a/Soft skills/Words.xlsx
+++ b/Soft skills/Words.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Working\Java Full Stack\Soft skills\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6841163-43C6-472F-8C0B-A167DBDA7716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09F365C-E4F7-49AF-98D3-1A193C391050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57107928-2823-472E-8A6E-F1A53761FD58}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="318">
   <si>
     <t>Word</t>
   </si>
@@ -916,6 +916,69 @@
   </si>
   <si>
     <t>His idea were not prevalent</t>
+  </si>
+  <si>
+    <t>Poses</t>
+  </si>
+  <si>
+    <t>to gain</t>
+  </si>
+  <si>
+    <t>to have something</t>
+  </si>
+  <si>
+    <t>poses</t>
+  </si>
+  <si>
+    <t>posed</t>
+  </si>
+  <si>
+    <t>seems</t>
+  </si>
+  <si>
+    <t>see</t>
+  </si>
+  <si>
+    <t>seem</t>
+  </si>
+  <si>
+    <t>saw</t>
+  </si>
+  <si>
+    <t>swat</t>
+  </si>
+  <si>
+    <t>relate</t>
+  </si>
+  <si>
+    <t>same</t>
+  </si>
+  <si>
+    <t>connects</t>
+  </si>
+  <si>
+    <t>comibine</t>
+  </si>
+  <si>
+    <t>To point out</t>
+  </si>
+  <si>
+    <t>highlight</t>
+  </si>
+  <si>
+    <t>give important</t>
+  </si>
+  <si>
+    <t>enfesize</t>
+  </si>
+  <si>
+    <t>avoid</t>
+  </si>
+  <si>
+    <t>neglait</t>
+  </si>
+  <si>
+    <t>not highlinghint</t>
   </si>
 </sst>
 </file>
@@ -3053,10 +3116,19 @@
       <c r="A220" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B220" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>1</v>
+      </c>
+      <c r="B221" t="s">
+        <v>298</v>
+      </c>
+      <c r="C221" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
@@ -3074,137 +3146,194 @@
         <v>45</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B225" t="s">
+        <v>300</v>
+      </c>
+      <c r="C225" t="s">
+        <v>301</v>
+      </c>
+      <c r="D225" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B227" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B232" t="s">
+        <v>303</v>
+      </c>
+      <c r="C232" t="s">
+        <v>304</v>
+      </c>
+      <c r="D232" t="s">
+        <v>305</v>
+      </c>
+      <c r="E232" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B234" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B235" t="s">
+        <v>308</v>
+      </c>
+      <c r="C235" t="s">
+        <v>309</v>
+      </c>
+      <c r="D235" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B241" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B242" t="s">
+        <v>311</v>
+      </c>
+      <c r="C242" t="s">
+        <v>312</v>
+      </c>
+      <c r="D242" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B243" t="s">
+        <v>315</v>
+      </c>
+      <c r="C243" t="s">
+        <v>316</v>
+      </c>
+      <c r="D243" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>1</v>
       </c>

--- a/Soft skills/Words.xlsx
+++ b/Soft skills/Words.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Working\Java Full Stack\Soft skills\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09F365C-E4F7-49AF-98D3-1A193C391050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAFE19A-0B8D-4B5B-9C9E-5F1CDE19FB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57107928-2823-472E-8A6E-F1A53761FD58}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1234" uniqueCount="359">
   <si>
     <t>Word</t>
   </si>
@@ -979,6 +979,129 @@
   </si>
   <si>
     <t>not highlinghint</t>
+  </si>
+  <si>
+    <t>Anticipate</t>
+  </si>
+  <si>
+    <t>To assume</t>
+  </si>
+  <si>
+    <t>To guess</t>
+  </si>
+  <si>
+    <t>To determine</t>
+  </si>
+  <si>
+    <t>To Predict</t>
+  </si>
+  <si>
+    <t>Anticate</t>
+  </si>
+  <si>
+    <t>Anticipated</t>
+  </si>
+  <si>
+    <t>Anticipating</t>
+  </si>
+  <si>
+    <t>Anticipation</t>
+  </si>
+  <si>
+    <t>We anticipated it wrong</t>
+  </si>
+  <si>
+    <t>it was our previeus anticipation</t>
+  </si>
+  <si>
+    <t>We should anticipate pros and cons of a decision making it</t>
+  </si>
+  <si>
+    <t>ML model anticipated wrong output</t>
+  </si>
+  <si>
+    <t>Blind</t>
+  </si>
+  <si>
+    <t>unpredicted</t>
+  </si>
+  <si>
+    <t>miss read</t>
+  </si>
+  <si>
+    <t>soodine</t>
+  </si>
+  <si>
+    <t>Acceptable</t>
+  </si>
+  <si>
+    <t>good for listening</t>
+  </si>
+  <si>
+    <t>Relaxing</t>
+  </si>
+  <si>
+    <t>Pleasing</t>
+  </si>
+  <si>
+    <t>pleasant</t>
+  </si>
+  <si>
+    <t>Shouting</t>
+  </si>
+  <si>
+    <t>Annoying</t>
+  </si>
+  <si>
+    <t>harsh</t>
+  </si>
+  <si>
+    <t>eye catchy</t>
+  </si>
+  <si>
+    <t>Captivating</t>
+  </si>
+  <si>
+    <t>likeable</t>
+  </si>
+  <si>
+    <t>dislike</t>
+  </si>
+  <si>
+    <t>unacceptable</t>
+  </si>
+  <si>
+    <t>he's voice is soodine</t>
+  </si>
+  <si>
+    <t>Charming</t>
+  </si>
+  <si>
+    <t>Her behaviur is likeable</t>
+  </si>
+  <si>
+    <t>hypothetical</t>
+  </si>
+  <si>
+    <t>imaginary</t>
+  </si>
+  <si>
+    <t>virtual</t>
+  </si>
+  <si>
+    <t>Obligate</t>
+  </si>
+  <si>
+    <t>Give an advice</t>
+  </si>
+  <si>
+    <t>Torch Bearer</t>
+  </si>
+  <si>
+    <t>guide</t>
+  </si>
+  <si>
+    <t>Who lead the way</t>
   </si>
 </sst>
 </file>
@@ -1345,13 +1468,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61498B0B-65E1-41EE-BDA5-1E9C4DD906D3}">
-  <dimension ref="A1:N273"/>
+  <dimension ref="A1:N1071"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="68.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="63.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="49.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="42.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="34.6640625" bestFit="1" customWidth="1"/>
@@ -3247,7 +3370,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>0</v>
       </c>
@@ -3255,7 +3378,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>1</v>
       </c>
@@ -3269,7 +3392,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>2</v>
       </c>
@@ -3283,134 +3406,3580 @@
         <v>317</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B248" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B249" t="s">
+        <v>319</v>
+      </c>
+      <c r="C249" t="s">
+        <v>320</v>
+      </c>
+      <c r="D249" t="s">
+        <v>321</v>
+      </c>
+      <c r="E249" t="s">
+        <v>322</v>
+      </c>
+      <c r="F249" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B250" t="s">
+        <v>331</v>
+      </c>
+      <c r="C250" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B251" t="s">
+        <v>327</v>
+      </c>
+      <c r="C251" t="s">
+        <v>328</v>
+      </c>
+      <c r="D251" t="s">
+        <v>329</v>
+      </c>
+      <c r="E251" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B253" t="s">
+        <v>323</v>
+      </c>
+      <c r="C253" t="s">
+        <v>324</v>
+      </c>
+      <c r="D253" t="s">
+        <v>325</v>
+      </c>
+      <c r="E253" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B255" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B256" t="s">
+        <v>335</v>
+      </c>
+      <c r="C256" t="s">
+        <v>336</v>
+      </c>
+      <c r="D256" t="s">
+        <v>337</v>
+      </c>
+      <c r="E256" t="s">
+        <v>338</v>
+      </c>
+      <c r="F256" t="s">
+        <v>339</v>
+      </c>
+      <c r="G256" t="s">
+        <v>343</v>
+      </c>
+      <c r="H256" t="s">
+        <v>344</v>
+      </c>
+      <c r="I256" t="s">
+        <v>345</v>
+      </c>
+      <c r="J256" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B257" t="s">
+        <v>340</v>
+      </c>
+      <c r="C257" t="s">
+        <v>341</v>
+      </c>
+      <c r="D257" t="s">
+        <v>342</v>
+      </c>
+      <c r="E257" t="s">
+        <v>346</v>
+      </c>
+      <c r="F257" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B258" t="s">
+        <v>348</v>
+      </c>
+      <c r="C258" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B262" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B263" t="s">
+        <v>352</v>
+      </c>
+      <c r="C263" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B269" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B270" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A275" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B275" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A276" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A277" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A278" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A279" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A282" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B282" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A283" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B283" t="s">
+        <v>357</v>
+      </c>
+      <c r="C283" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A284" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A285" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A286" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A288" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A289" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A290" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A291" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A292" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A294" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A295" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A296" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A297" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A298" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A300" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A301" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A302" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A303" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A304" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A306" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A307" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A308" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A309" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A310" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A312" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A313" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A314" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A315" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A316" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A318" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A319" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A320" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A321" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A322" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A324" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A325" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A326" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A327" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A328" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A330" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A331" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A332" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A333" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A334" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A336" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A337" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A338" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A339" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A340" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A342" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A343" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A344" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A345" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A346" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A348" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A349" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A350" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A351" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A352" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A354" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A355" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A356" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A357" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A358" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A360" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A361" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A362" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A363" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A364" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A366" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A367" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A368" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A369" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A370" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A372" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A373" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A374" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A375" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A376" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A378" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A379" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A380" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A381" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A382" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A384" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A385" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A386" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A387" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A388" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A390" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A391" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A392" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A393" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A394" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A396" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A397" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A398" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A399" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A400" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A402" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A403" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A404" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A405" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A406" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A408" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A409" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A410" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A411" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A412" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A414" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A415" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A416" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A417" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A418" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A420" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A421" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A422" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A423" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A424" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A426" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A427" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A428" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A429" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A430" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A432" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A433" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A434" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A435" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A436" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A438" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A439" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A440" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A441" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A442" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A444" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A445" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A446" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A447" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A448" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A450" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A451" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A452" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A453" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A454" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A456" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A457" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A458" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A459" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A460" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A462" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A463" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A464" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A465" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A466" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A468" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A469" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A470" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A471" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A472" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A474" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A475" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A476" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A477" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A478" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A480" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A481" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A482" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A483" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A484" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A486" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A487" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A488" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A489" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A490" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A492" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A493" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A494" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A495" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A496" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="498" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A498" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A499" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="500" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A500" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="501" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A501" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="502" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A502" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="504" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A504" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A505" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="506" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A506" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A507" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="508" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A508" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="510" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A510" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A511" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="512" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A512" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A513" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A514" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A516" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A517" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="518" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A518" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="519" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A519" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="520" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A520" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="522" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A522" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A523" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="524" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A524" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="525" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A525" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="526" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A526" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="528" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A528" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A529" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="530" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A530" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="531" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A531" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="532" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A532" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="534" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A534" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A535" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="536" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A536" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="537" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A537" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="538" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A538" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="540" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A540" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A541" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="542" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A542" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="543" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A543" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="544" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A544" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="546" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A546" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A547" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="548" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A548" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="549" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A549" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="550" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A550" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="552" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A552" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A553" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="554" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A554" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="555" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A555" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="556" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A556" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="558" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A558" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A559" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="560" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A560" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="561" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A561" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="562" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A562" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="564" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A564" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="565" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A565" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="566" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A566" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="567" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A567" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="568" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A568" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="570" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A570" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A571" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="572" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A572" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="573" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A573" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="574" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A574" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="576" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A576" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A577" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="578" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A578" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="579" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A579" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="580" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A580" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="582" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A582" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A583" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="584" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A584" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="585" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A585" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="586" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A586" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="588" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A588" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="589" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A589" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="590" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A590" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="591" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A591" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="592" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A592" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="594" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A594" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="595" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A595" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="596" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A596" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="597" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A597" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="598" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A598" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="600" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A600" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="601" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A601" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="602" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A602" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="603" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A603" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="604" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A604" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="606" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A606" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A607" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="608" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A608" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="609" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A609" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="610" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A610" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="612" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A612" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="613" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A613" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="614" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A614" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="615" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A615" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="616" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A616" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="618" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A618" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A619" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="620" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A620" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="621" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A621" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="622" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A622" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="624" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A624" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A625" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="626" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A626" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="627" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A627" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="628" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A628" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="630" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A630" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="631" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A631" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="632" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A632" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="633" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A633" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="634" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A634" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="636" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A636" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="637" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A637" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="638" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A638" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="639" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A639" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="640" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A640" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="642" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A642" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A643" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="644" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A644" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="645" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A645" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="646" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A646" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="648" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A648" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="649" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A649" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="650" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A650" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="651" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A651" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="652" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A652" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="654" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A654" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="655" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A655" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="656" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A656" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="657" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A657" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="658" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A658" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="660" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A660" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="661" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A661" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="662" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A662" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="663" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A663" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="664" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A664" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="666" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A666" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="667" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A667" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="668" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A668" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="669" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A669" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="670" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A670" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="672" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A672" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="673" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A673" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="674" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A674" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="675" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A675" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="676" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A676" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="678" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A678" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="679" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A679" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="680" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A680" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="681" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A681" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="682" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A682" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="684" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A684" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="685" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A685" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="686" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A686" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="687" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A687" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="688" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A688" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="690" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A690" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="691" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A691" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="692" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A692" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="693" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A693" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="694" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A694" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="696" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A696" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="697" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A697" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="698" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A698" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="699" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A699" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="700" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A700" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="702" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A702" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="703" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A703" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="704" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A704" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="705" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A705" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="706" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A706" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="708" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A708" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="709" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A709" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="710" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A710" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="711" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A711" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="712" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A712" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="714" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A714" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="715" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A715" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="716" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A716" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="717" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A717" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="718" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A718" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="720" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A720" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="721" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A721" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="722" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A722" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="723" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A723" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="724" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A724" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="726" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A726" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="727" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A727" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="728" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A728" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="729" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A729" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="730" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A730" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="732" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A732" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="733" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A733" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="734" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A734" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="735" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A735" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="736" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A736" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="738" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A738" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="739" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A739" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="740" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A740" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="741" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A741" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="742" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A742" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="744" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A744" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="745" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A745" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="746" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A746" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="747" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A747" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="748" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A748" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="750" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A750" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="751" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A751" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="752" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A752" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="753" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A753" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="754" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A754" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="756" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A756" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="757" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A757" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="758" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A758" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="759" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A759" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="760" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A760" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="762" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A762" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="763" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A763" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="764" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A764" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="765" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A765" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="766" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A766" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="768" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A768" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="769" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A769" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="770" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A770" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="771" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A771" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="772" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A772" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="774" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A774" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="775" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A775" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="776" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A776" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="777" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A777" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="778" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A778" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="780" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A780" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="781" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A781" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="782" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A782" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="783" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A783" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="784" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A784" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="786" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A786" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="787" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A787" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="788" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A788" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="789" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A789" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="790" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A790" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="792" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A792" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="793" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A793" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="794" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A794" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="795" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A795" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="796" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A796" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="798" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A798" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="799" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A799" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="800" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A800" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="801" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A801" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="802" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A802" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="804" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A804" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="805" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A805" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="806" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A806" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="807" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A807" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="808" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A808" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="810" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A810" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="811" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A811" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="812" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A812" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="813" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A813" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="814" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A814" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="816" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A816" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="817" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A817" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="818" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A818" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="819" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A819" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="820" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A820" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="822" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A822" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="823" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A823" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="824" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A824" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="825" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A825" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="826" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A826" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="828" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A828" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="829" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A829" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="830" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A830" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="831" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A831" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="832" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A832" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="834" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A834" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="835" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A835" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="836" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A836" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="837" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A837" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="838" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A838" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="840" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A840" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="841" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A841" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="842" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A842" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="843" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A843" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="844" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A844" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="846" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A846" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="847" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A847" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="848" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A848" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="849" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A849" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="850" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A850" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="852" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A852" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="853" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A853" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="854" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A854" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="855" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A855" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="856" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A856" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="858" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A858" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="859" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A859" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="860" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A860" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="861" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A861" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="862" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A862" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="864" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A864" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="865" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A865" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="866" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A866" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="867" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A867" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="868" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A868" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="870" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A870" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="871" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A871" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="872" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A872" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="873" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A873" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="874" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A874" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="876" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A876" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="877" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A877" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="878" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A878" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="879" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A879" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="880" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A880" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="882" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A882" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="883" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A883" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="884" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A884" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="885" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A885" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="886" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A886" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="888" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A888" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="889" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A889" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="890" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A890" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="891" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A891" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="892" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A892" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="894" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A894" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="895" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A895" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="896" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A896" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="897" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A897" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="898" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A898" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="900" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A900" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="901" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A901" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="902" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A902" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="903" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A903" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="904" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A904" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="906" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A906" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="907" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A907" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="908" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A908" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="909" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A909" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="910" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A910" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="912" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A912" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="913" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A913" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="914" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A914" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="915" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A915" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="916" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A916" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="918" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A918" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="919" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A919" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="920" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A920" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="921" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A921" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="922" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A922" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="924" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A924" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="925" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A925" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="926" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A926" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="927" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A927" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="928" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A928" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="930" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A930" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="931" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A931" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="932" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A932" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="933" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A933" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="934" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A934" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="936" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A936" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="937" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A937" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="938" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A938" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="939" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A939" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="940" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A940" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="942" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A942" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="943" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A943" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="944" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A944" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="945" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A945" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="946" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A946" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="948" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A948" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="949" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A949" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="950" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A950" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="951" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A951" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="952" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A952" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="954" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A954" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="955" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A955" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="956" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A956" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="957" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A957" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="958" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A958" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="960" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A960" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="961" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A961" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="962" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A962" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="963" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A963" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="964" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A964" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="966" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A966" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="967" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A967" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="968" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A968" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="969" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A969" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="970" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A970" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="972" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A972" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="973" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A973" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="974" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A974" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="975" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A975" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="976" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A976" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="978" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A978" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="979" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A979" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="980" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A980" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="981" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A981" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="982" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A982" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="984" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A984" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="985" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A985" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="986" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A986" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="987" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A987" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="988" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A988" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="990" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A990" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="991" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A991" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="992" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A992" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="993" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A993" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="994" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A994" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="996" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A996" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="997" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A997" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="998" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A998" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="999" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A999" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1000" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1002" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1003" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1004" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1005" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1006" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1008" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1009" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1010" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1011" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1012" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1014" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1015" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1016" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1017" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1018" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1020" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1021" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1022" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1023" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1024" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1026" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1027" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1028" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1029" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1030" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1032" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1033" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1034" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1035" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1036" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1038" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1039" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1040" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1041" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1042" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1044" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1045" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1046" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1047" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1048" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1050" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1051" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1052" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1053" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1054" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1056" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1057" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1058" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1059" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1060" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1062" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1063" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1064" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1065" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1066" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1068" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1069" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1070" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1071" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Soft skills/Words.xlsx
+++ b/Soft skills/Words.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Working\Java Full Stack\Soft skills\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAFE19A-0B8D-4B5B-9C9E-5F1CDE19FB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF6A4138-EEA2-4D3D-879A-F922168A6261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57107928-2823-472E-8A6E-F1A53761FD58}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1234" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="377">
   <si>
     <t>Word</t>
   </si>
@@ -1102,6 +1102,60 @@
   </si>
   <si>
     <t>Who lead the way</t>
+  </si>
+  <si>
+    <t>resonate</t>
+  </si>
+  <si>
+    <t>to connect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to relate </t>
+  </si>
+  <si>
+    <t>to Attach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to align with </t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resonating </t>
+  </si>
+  <si>
+    <t>Resonate</t>
+  </si>
+  <si>
+    <t>ditatch</t>
+  </si>
+  <si>
+    <t>disjoin</t>
+  </si>
+  <si>
+    <t>tense helps us to resonate with how when and where</t>
+  </si>
+  <si>
+    <t>He crowded loud to resonate with peoples</t>
+  </si>
+  <si>
+    <t>The viruses are resonated with software sometimes</t>
+  </si>
+  <si>
+    <t>nail</t>
+  </si>
+  <si>
+    <t>Do something great</t>
+  </si>
+  <si>
+    <t>Did something good</t>
+  </si>
+  <si>
+    <t>browe</t>
+  </si>
+  <si>
+    <t>outstanding</t>
   </si>
 </sst>
 </file>
@@ -3716,73 +3770,130 @@
       <c r="A288" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B288" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B289" t="s">
+        <v>360</v>
+      </c>
+      <c r="C289" t="s">
+        <v>361</v>
+      </c>
+      <c r="D289" t="s">
+        <v>362</v>
+      </c>
+      <c r="E289" t="s">
+        <v>363</v>
+      </c>
+      <c r="F289" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B290" t="s">
+        <v>215</v>
+      </c>
+      <c r="C290" t="s">
+        <v>367</v>
+      </c>
+      <c r="D290" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B291" t="s">
+        <v>369</v>
+      </c>
+      <c r="C291" t="s">
+        <v>370</v>
+      </c>
+      <c r="D291" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B292" t="s">
+        <v>365</v>
+      </c>
+      <c r="C292" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B294" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B295" t="s">
+        <v>373</v>
+      </c>
+      <c r="C295" t="s">
+        <v>374</v>
+      </c>
+      <c r="D295" t="s">
+        <v>375</v>
+      </c>
+      <c r="E295" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>45</v>
       </c>
